--- a/backtest_runs/20260410_193731/by_symbol/NBP/NBP.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/NBP/NBP.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-4145.519999999995</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>95854.48000000001</v>
@@ -633,7 +633,7 @@
         <v>-772.7999999999874</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>95081.68000000002</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>95081.68000000002</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>106381.12</v>
@@ -863,7 +863,7 @@
         <v>-298.0799999999956</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>106083.04</v>
@@ -909,7 +909,7 @@
         <v>-8197.200000000012</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>97885.84000000001</v>
@@ -955,7 +955,7 @@
         <v>-21207.83999999999</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>76678.00000000001</v>
@@ -1001,7 +1001,7 @@
         <v>-2997.360000000004</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>73680.64000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-1794</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>71886.64000000001</v>
@@ -1093,7 +1093,7 @@
         <v>-1633.919999999989</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>70252.72000000003</v>
@@ -1185,7 +1185,7 @@
         <v>-5111.519999999995</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>65141.20000000003</v>
@@ -1231,7 +1231,7 @@
         <v>-3477.600000000006</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>61663.60000000002</v>
@@ -1277,7 +1277,7 @@
         <v>-6243.120000000001</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>55420.48000000002</v>
@@ -1415,7 +1415,7 @@
         <v>-5083.919999999989</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>63556.96000000003</v>
@@ -1461,7 +1461,7 @@
         <v>-1098.480000000005</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>62458.48000000003</v>
@@ -1507,7 +1507,7 @@
         <v>-182.1600000000069</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>62276.32000000002</v>
@@ -1553,7 +1553,7 @@
         <v>-1374.479999999989</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>60901.84000000003</v>
